--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.30303209574707</v>
+        <v>6.711742715558899</v>
       </c>
       <c r="D2" t="n">
-        <v>39.9817265826686</v>
+        <v>6.497030569683647</v>
       </c>
       <c r="E2" t="n">
-        <v>12.00084561557008</v>
+        <v>1.950137412530139</v>
       </c>
       <c r="F2" t="n">
-        <v>11.54354194893672</v>
+        <v>1.875825566702217</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.15940617165391</v>
+        <v>6.20090350289376</v>
       </c>
       <c r="D3" t="n">
-        <v>17.3320926176972</v>
+        <v>2.816465050375795</v>
       </c>
       <c r="E3" t="n">
-        <v>12.00084561557008</v>
+        <v>1.950137412530139</v>
       </c>
       <c r="F3" t="n">
-        <v>11.54354194893672</v>
+        <v>1.875825566702217</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.06689255600174</v>
+        <v>3.748370040350282</v>
       </c>
       <c r="D4" t="n">
-        <v>9.216597921046922</v>
+        <v>1.497697162170125</v>
       </c>
       <c r="E4" t="n">
-        <v>12.00084561557008</v>
+        <v>1.950137412530139</v>
       </c>
       <c r="F4" t="n">
-        <v>11.54354194893672</v>
+        <v>1.875825566702217</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.72782123758696</v>
+        <v>1.905770951107881</v>
       </c>
       <c r="D5" t="n">
-        <v>11.53659727031777</v>
+        <v>1.874697056426638</v>
       </c>
       <c r="E5" t="n">
-        <v>12.00084561557008</v>
+        <v>1.950137412530139</v>
       </c>
       <c r="F5" t="n">
-        <v>11.54354194893672</v>
+        <v>1.875825566702217</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.99832971616928</v>
+        <v>4.874728578877508</v>
       </c>
       <c r="D6" t="n">
-        <v>29.93197981836165</v>
+        <v>4.863946720483769</v>
       </c>
       <c r="E6" t="n">
-        <v>12.00084561557008</v>
+        <v>1.950137412530139</v>
       </c>
       <c r="F6" t="n">
-        <v>11.54354194893672</v>
+        <v>1.875825566702217</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>3.575256918027836</v>
+        <v>0.5809792491795234</v>
       </c>
       <c r="D7" t="n">
-        <v>3.614061873952854</v>
+        <v>0.5872850545173387</v>
       </c>
       <c r="E7" t="n">
-        <v>12.00084561557008</v>
+        <v>1.950137412530139</v>
       </c>
       <c r="F7" t="n">
-        <v>11.54354194893672</v>
+        <v>1.875825566702217</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.23757971278654</v>
+        <v>4.913606703327813</v>
       </c>
       <c r="D8" t="n">
-        <v>30.24608672687099</v>
+        <v>4.914989093116536</v>
       </c>
       <c r="E8" t="n">
-        <v>12.00084561557008</v>
+        <v>1.950137412530139</v>
       </c>
       <c r="F8" t="n">
-        <v>11.54354194893672</v>
+        <v>1.875825566702217</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.2862790187984</v>
+        <v>3.29652034055474</v>
       </c>
       <c r="D9" t="n">
-        <v>19.93246607483401</v>
+        <v>3.239025737160527</v>
       </c>
       <c r="E9" t="n">
-        <v>12.00084561557008</v>
+        <v>1.950137412530139</v>
       </c>
       <c r="F9" t="n">
-        <v>11.54354194893672</v>
+        <v>1.875825566702217</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
